--- a/docs/planning/QA엑셀-v1/이혜린/QA 담양 중대재해 위험성평가 이혜린.xlsx
+++ b/docs/planning/QA엑셀-v1/이혜린/QA 담양 중대재해 위험성평가 이혜린.xlsx
@@ -19,11 +19,11 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'1 정기평가 만들기'!$A$3:$I$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'1 정기평가 만들기'!$3:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2 설문조사표·보고서'!$A$3:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2 설문조사표·보고서'!$A$3:$I$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'2 설문조사표·보고서'!$3:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3 전달·조치·확인'!$A$3:$I$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3 전달·조치·확인'!$A$3:$I$18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'3 전달·조치·확인'!$3:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'4 공문·결재'!$A$3:$I$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'4 공문·결재'!$A$3:$I$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'4 공문·결재'!$3:$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'5 수시평가'!$A$3:$I$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'5 수시평가'!$3:$3</definedName>
@@ -37,7 +37,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,9 +61,9 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <i val="1"/>
-      <color rgb="007F7F7F"/>
+      <color rgb="000563C1"/>
       <sz val="10.5"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -116,6 +116,12 @@
     <font>
       <name val="맑은 고딕"/>
       <color rgb="00A6A6A6"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <i val="1"/>
+      <color rgb="007F7F7F"/>
       <sz val="10.5"/>
     </font>
   </fonts>
@@ -271,6 +277,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -289,10 +298,7 @@
     <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -790,7 +796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -849,12 +855,12 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>이 파일</t>
+          <t>내 계정</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>정기 위험성평가를 만들고 → 부서가 조치하고 → 재난안전과가 확인하고 → 공문까지 올리는 흐름, 그리고 수시 위험성평가를 봅니다.</t>
+          <t>QA박안전6 (재난안전과 담당자) · QA하정수6 (내 부서 문화체육과 담당 공무원)</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -867,12 +873,12 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>줄 수</t>
+          <t>정기평가 진행자</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>53줄</t>
+          <t>나 — 진행자만 하는 줄 10개가 이 파일에 들어 있습니다(«누구로»에 «(진행자)»)</t>
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -882,15 +888,15 @@
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="5" t="n"/>
     </row>
-    <row r="7" ht="22" customHeight="1">
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>시트</t>
+          <t>이 파일</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>1 정기평가 만들기 → 2 설문조사표·보고서 → 3 전달·조치·확인 → 4 공문·결재 → 5 수시평가</t>
+          <t>정기 위험성평가 1건을 6명이 함께 진행하고(만들기 → 내 부서 제출·조치 → 재난안전과 확인 → 공문), 수시 위험성평가는 각자 합니다. 개발자에게 받은 계정 두 개(QA박안전6 · QA하정수6)만 씁니다.</t>
         </is>
       </c>
       <c r="C7" s="4" t="n"/>
@@ -903,12 +909,12 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>테스트 주소</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>(배포 주소를 받으면 채웁니다)</t>
+          <t>줄 수</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>54줄</t>
         </is>
       </c>
       <c r="C8" s="4" t="n"/>
@@ -921,10 +927,14 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>브라우저</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
+          <t>시트</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>1 정기평가 만들기 → 2 설문조사표·보고서 → 3 전달·조치·확인 → 4 공문·결재 → 5 수시평가</t>
+        </is>
+      </c>
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
@@ -935,10 +945,14 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>기기</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n"/>
+          <t>테스트 주소</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>https://safety.damyang.go.kr/login</t>
+        </is>
+      </c>
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
@@ -949,10 +963,10 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>시작한 날</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n"/>
+          <t>브라우저</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
@@ -960,523 +974,935 @@
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="5" t="n"/>
     </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>기기</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>시작한 날</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="5" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>이렇게 하면 됩니다</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>① 브라우저로 위 «테스트 주소»를 엽니다. 시트마다 맨 위에 «새 탭에서 시작» 또는 «같은 탭에서 이어서»가 적혀 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="21" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>② 화면 오른쪽 위 이름을 눌러 «누구로» 칸의 사람으로 바꿉니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="21" customHeight="1">
+    <row r="16" ht="36" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>③ «어디서» 메뉴로 가서 «해 볼 것»대로 눌러 봅니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="21" customHeight="1">
+          <t>① 위 «테스트 주소»에서 받은 아이디·비밀번호로 로그인합니다. 로그인하면 통합 현황 화면으로 갑니다. 5번 틀리면 계정이 잠깁니다 — 담당 개발자에게 풀어 달라고 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>④ «이러면 성공»과 같으면 «결과» 칸에서 성공을, 다르면 실패·오류 등을 고릅니다.</t>
+          <t>② 내 계정 두 개를 창 두 개에 따로 로그인해 둡니다 — 일반 창에는 QA박안전6(재난안전과), 시크릿 창(Ctrl + Shift + N · 맥 Cmd + Shift + N)에는 QA하정수6(담당 공무원). 두 창을 나란히 두면 계정을 바꿀 필요가 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
+          <t>③ «누구로» 칸에 적힌 계정의 창에서 «어디서» 메뉴로 가서 «해 볼 것»대로 눌러 봅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>④ «이러면 성공»과 같으면 «결과» 칸에서 성공을, 다르면 실패·오류 등을 고릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="21" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
           <t>⑤ 실패·오류·문의면 «메모»에 한 줄 적고, 필요하면 «사진» 칸에 화면 캡처를 붙여넣습니다.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>결과 고르는 법</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>결과</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>이럴 때 고르세요</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>«이러면 성공»대로 된다</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>되긴 하는데 설명과 다르다 — 막혀야 하는데 저장된다, 문구·숫자가 틀리다</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>오류</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>화면이 멈추거나 깨진다, 눌러도 아무 일이 없다, 오류 창이 뜬다</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>앞 단계가 안 돼서 지금은 못 한다 — 메모에 이유</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="5" t="n"/>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>정기평가는 6명이 함께 — 진행 순서</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>• 정기평가는 한 해에 1건만 만들 수 있어서 6명이 한 건을 함께 진행합니다. 평가 전체에 한 번만 하는 일(만들기·양식·보고서·전달·공문)은 진행자(이혜린)가 하고, 나머지는 각자 내 부서(문화체육과) 일을 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>• 대상 부서: 물순환사업소 · 건설과 · 공공시설사업소 · 담양읍 · 보건소 · 문화체육과 · 환경과 (7개). 마지막 부서(환경과)에는 담당 공무원 계정이 없어서 진행자가 대신 처리합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="21" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>• 아래 신호가 단체방에 올라오면 다음으로 넘어갑니다. 신호를 기다리지 않는 줄은 먼저 해도 됩니다.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>이 환경에서는 볼 수 없다 — 예: 확인할 데이터가 없다</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>순서</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>누가</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>끝나면 단체방에</t>
+        </is>
+      </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n"/>
     </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>문의</t>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>맞는지 헷갈린다 — 메모에 궁금한 점</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
+          <t>모두</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>1번 시트 1~6번 (만들기 창은 [취소]로 닫기)</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>«만들기 전 확인 끝»</t>
+        </is>
+      </c>
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="5" t="n"/>
     </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>사진 붙이는 법</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="21" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>• 윈도우: Win + Shift + S → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Ctrl + V</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="21" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>• 맥: Cmd + Ctrl + Shift + 4 → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Cmd + V</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="21" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>• 사진이 크면 모서리를 끌어 줄이세요. 사진은 그 줄 «사진» 칸 위에 두면 됩니다 — 취합할 때 줄 번호로 찾습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="21" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>• 사진은 떠 있는 그대로 두세요(«셀에 배치»로 넣으면 취합할 때 꺼내지 못합니다).</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>누구로 — 계정 바꾸는 법</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="21" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>• 화면 오른쪽 위 이름을 누르면 사람 목록이 나옵니다. «누구로» 칸의 이름을 누르면 바뀝니다.</t>
-        </is>
-      </c>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>진행자</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>평가 만들기</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>«평가 만듦»</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>진행자</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>설문조사표 양식 올리기</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>«양식 올림»</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>모두</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>내 부서 작성본 제출</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>«제출 끝»</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>진행자</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>보고서 올리기</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>«보고서 올림»</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>모두</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>내 부서 개선조치 적기</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>«개선조치 적음»</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>진행자</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>부서로 전달</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>«전달함»</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>모두</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>조치 완료 · 확인 · 반려 · 재제출</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>«확인 끝»</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>모두</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>결재선 확인 (상신하지 않기)</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>«결재선 확인 끝»</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="5" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>진행자</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>공문 상신</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>«상신함»</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="5" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>이름</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>누구</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>주로 하는 것</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="n"/>
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>모두</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>상신 뒤 잠김 확인</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>«잠김 확인 끝»</t>
+        </is>
+      </c>
       <c r="G37" s="4" t="n"/>
       <c r="H37" s="5" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>박안전</t>
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>재난안전과 담당자</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>대부분 이 계정 — 등록·확인·공문</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="n"/>
+          <t>진행자</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>결재 상태 확인</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>«결재 완료 확인»</t>
+        </is>
+      </c>
       <c r="G38" s="4" t="n"/>
       <c r="H38" s="5" t="n"/>
     </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="17" t="inlineStr">
-        <is>
-          <t>하정수</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>물순환사업소 담당자</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>자기 부서 일만 한다</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n"/>
-      <c r="G39" s="4" t="n"/>
-      <c r="H39" s="5" t="n"/>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>정환경</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>환경과 담당자</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>남의 부서 것을 못 건드리는지 볼 때</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="5" t="n"/>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="17" t="inlineStr">
-        <is>
-          <t>오순환</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>물순환사업소장</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>자기 부서를 보고 재촉한다</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="n"/>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="5" t="n"/>
+    <row r="39" ht="21" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>• 수시평가(5번 시트)는 순서와 상관없이 아무 때나 해도 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>결과 고르는 법</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>김중대</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>중대재해팀장</t>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>결과</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>이럴 때 고르세요</t>
         </is>
       </c>
       <c r="C42" s="4" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>공문 결재선(검토)을 볼 때</t>
-        </is>
-      </c>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
       <c r="F42" s="4" t="n"/>
       <c r="G42" s="4" t="n"/>
       <c r="H42" s="5" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>홍길동</t>
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>성공</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>재난안전과장</t>
+          <t>«이러면 성공»대로 된다</t>
         </is>
       </c>
       <c r="C43" s="4" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>보기만 한다 — 등록 버튼이 없는 게 정상</t>
-        </is>
-      </c>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
       <c r="F43" s="4" t="n"/>
       <c r="G43" s="4" t="n"/>
       <c r="H43" s="5" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="17" t="inlineStr">
-        <is>
-          <t>김담양</t>
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>실패</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>군수</t>
+          <t>되긴 하는데 설명과 다르다 — 막혀야 하는데 저장된다, 문구·숫자가 틀리다</t>
         </is>
       </c>
       <c r="C44" s="4" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>보기만 한다</t>
-        </is>
-      </c>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="n"/>
       <c r="G44" s="4" t="n"/>
       <c r="H44" s="5" t="n"/>
     </row>
-    <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>알아 두면 좋은 것 (결함이 아닙니다)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="21" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>• 오늘 날짜가 2026-07-16 으로 고정돼 있습니다. 기한·D-day는 이 날 기준입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="21" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>• 입력한 데이터는 그 브라우저 탭에만 남습니다. 새 탭을 열면 처음 상태로 돌아갑니다(새로고침은 괜찮습니다).</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="21" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>• 파일 첨부는 파일 이름만 남습니다. 실제 파일을 열거나 받을 수는 없습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="21" customHeight="1">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>• «…연계 후 제공됩니다» 안내는 일부러 막아 둔 기능입니다.</t>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>오류</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>화면이 멈추거나 깨진다, 눌러도 아무 일이 없다, 오류 창이 뜬다</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="5" t="n"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>앞 단계가 안 돼서 지금은 못 한다 — 메모에 이유</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="5" t="n"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>이 환경에서는 볼 수 없다 — 예: 확인할 데이터가 없다</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="4" t="n"/>
+      <c r="H47" s="5" t="n"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>문의</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>맞는지 헷갈린다 — 메모에 궁금한 점</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" s="4" t="n"/>
+      <c r="H48" s="5" t="n"/>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>사진 붙이는 법</t>
         </is>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>• 과장·군수에게 등록·수정 버튼이 없는 것, 결재 승인·반려 버튼이 없는 것(결재는 온나라에서 합니다)은 정상입니다.</t>
+          <t>• 윈도우: Win + Shift + S → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Ctrl + V</t>
         </is>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>• 2025년 자료는 실제 문서이고, 2026년 자료는 «예시 자료»입니다.</t>
+          <t>• 맥: Cmd + Ctrl + Shift + 4 → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Cmd + V</t>
         </is>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>• ---</t>
+          <t>• 사진이 크면 모서리를 끌어 줄이세요. 사진은 그 줄 «사진» 칸 위에 두면 됩니다 — 취합할 때 줄 번호로 찾습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="21" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>• 사진은 떠 있는 그대로 두세요(«셀에 배치»로 넣으면 취합할 때 꺼내지 못합니다).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>누구로 — 내 계정 두 개</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="21" customHeight="1">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>• 계정은 두 개뿐입니다. «누구로» 칸에 계정 이름과 권한이 함께 적혀 있습니다. 비밀번호는 따로 받습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>권한</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>볼 수 있는 것</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>주로 하는 것</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="5" t="n"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>QA박안전6</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>재난안전과 담당자</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>모든 부서 · «내 할일»은 전체</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>전 부서 등록·수정 · 확인 · 상신 · 독촉 — 대부분 이 계정</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n"/>
+      <c r="H59" s="5" t="n"/>
+    </row>
+    <row r="60" ht="51" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>QA하정수6</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>담당 공무원 (내 부서: 문화체육과)</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="n"/>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>업무 화면은 전 부서, «내 할일»은 나에게 지정된 것만, 위험성평가 부서별 조치표·교육 이수현황은 내 부서만</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>내 부서 일 · 남의 부서 것을 못 건드리는지 확인</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n"/>
+      <c r="H60" s="5" t="n"/>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>QA시스템관리</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>시스템 관리자 (김유석만)</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>시스템 관리 메뉴</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>시스템 관리 파일 · 공문 반려(결재 대행)</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="n"/>
+      <c r="H61" s="5" t="n"/>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>같은 서버를 6명이 함께 씁니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="21" customHeight="1">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>• 내가 만드는 것(교육 · 근로자 · 문서 · 위원 등)은 이름 앞에 내 이름을 붙입니다 — 예: «이혜린_집합교육». 그래야 내 것을 찾기 쉽습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="21" customHeight="1">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>• 다른 사람이 만든 것은 고치거나 지우지 않습니다. QA박안전6 계정에는 남의 것도 보이는데, 정상입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="21" customHeight="1">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>• 건수·이수율 같은 숫자는 다른 사람이 작업하는 동안 바뀔 수 있습니다. 숫자가 안 맞으면 새로고침해서 한 번 더 보고, 그래도 다르면 «실패».</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="24" customHeight="1">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>알아 두면 좋은 것 (결함이 아닙니다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="21" customHeight="1">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>• 기한·D-day는 서버의 오늘 날짜 기준입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="21" customHeight="1">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>• «…연계 후 제공됩니다» 안내는 일부러 막아 둔 기능입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="21" customHeight="1">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>• «이러면 성공»의 «» 안 문구와 화면 글자가 조금 다르고(띄어쓰기·마침표·어순) 뜻이 같으면 «문의»로 고르고 화면 문구를 메모에 적습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="21" customHeight="1">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>• 온나라 연계 전까지 결재는 시스템 안에서 끝납니다 — 상신하면 바로 «결재완료»가 되고 «내부 처리»로 표시됩니다. 결재자가 로그인해 승인할 일은 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="21" customHeight="1">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>• 로그인은 30분이 지나면 끊깁니다(작업 중이어도). 다시 로그인하고 이어서 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="21" customHeight="1">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>• 독촉·재촉 알림은 실제 직원에게 가고 되돌릴 수 없습니다. 내 부서 건만 1건씩 누릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="21" customHeight="1">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>• 과장·팀장이 담당자를 지정하는 흐름과 «내 할일»의 ‹자기 부서 전체› 보기는 과장 계정이 없어 이번 QA 범위 밖입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="21" customHeight="1">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>• 순서를 놓쳤거나 확인할 자료가 서버에 없으면 «확인 불가»를 고르고 메모에 이유를 적습니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A30:H30"/>
+  <mergeCells count="95">
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A69:H69"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A72:H72"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="F59:H59"/>
     <mergeCell ref="B9:H9"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="A70:H70"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="F58:H58"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="A74:H74"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A71:H71"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="B48:H48"/>
+    <mergeCell ref="A76:H76"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="B59:C59"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="A65:H65"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="A23:H23"/>
     <mergeCell ref="A52:H52"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D59:E59"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"크롬,엣지,웨일,사파리,파이어폭스,기타"</formula1>
     </dataValidation>
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"윈도우 PC,맥,태블릿,휴대폰"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1619,36 +2045,36 @@
         </is>
       </c>
       <c r="B6" s="21">
-        <f>COUNTA('2 설문조사표·보고서'!$A$4:$A$13)</f>
-        <v>10</v>
+        <f>COUNTA('2 설문조사표·보고서'!$A$4:$A$14)</f>
+        <v>11</v>
       </c>
       <c r="C6" s="21">
-        <f>COUNTIF('2 설문조사표·보고서'!$G$4:$G$13,"성공")</f>
+        <f>COUNTIF('2 설문조사표·보고서'!$G$4:$G$14,"성공")</f>
         <v>0</v>
       </c>
       <c r="D6" s="21">
-        <f>COUNTIF('2 설문조사표·보고서'!$G$4:$G$13,"실패")</f>
+        <f>COUNTIF('2 설문조사표·보고서'!$G$4:$G$14,"실패")</f>
         <v>0</v>
       </c>
       <c r="E6" s="21">
-        <f>COUNTIF('2 설문조사표·보고서'!$G$4:$G$13,"오류")</f>
+        <f>COUNTIF('2 설문조사표·보고서'!$G$4:$G$14,"오류")</f>
         <v>0</v>
       </c>
       <c r="F6" s="21">
-        <f>COUNTIF('2 설문조사표·보고서'!$G$4:$G$13,"보류")</f>
+        <f>COUNTIF('2 설문조사표·보고서'!$G$4:$G$14,"보류")</f>
         <v>0</v>
       </c>
       <c r="G6" s="21">
-        <f>COUNTIF('2 설문조사표·보고서'!$G$4:$G$13,"확인 불가")</f>
+        <f>COUNTIF('2 설문조사표·보고서'!$G$4:$G$14,"확인 불가")</f>
         <v>0</v>
       </c>
       <c r="H6" s="21">
-        <f>COUNTIF('2 설문조사표·보고서'!$G$4:$G$13,"문의")</f>
+        <f>COUNTIF('2 설문조사표·보고서'!$G$4:$G$14,"문의")</f>
         <v>0</v>
       </c>
       <c r="I6" s="21">
-        <f>COUNTBLANK('2 설문조사표·보고서'!$G$4:$G$13)</f>
-        <v>10</v>
+        <f>COUNTBLANK('2 설문조사표·보고서'!$G$4:$G$14)</f>
+        <v>11</v>
       </c>
       <c r="J6" s="22">
         <f>IF(B6=0,0,(B6-I6)/B6)</f>
@@ -1662,36 +2088,36 @@
         </is>
       </c>
       <c r="B7" s="21">
-        <f>COUNTA('3 전달·조치·확인'!$A$4:$A$19)</f>
-        <v>16</v>
+        <f>COUNTA('3 전달·조치·확인'!$A$4:$A$18)</f>
+        <v>15</v>
       </c>
       <c r="C7" s="21">
-        <f>COUNTIF('3 전달·조치·확인'!$G$4:$G$19,"성공")</f>
+        <f>COUNTIF('3 전달·조치·확인'!$G$4:$G$18,"성공")</f>
         <v>0</v>
       </c>
       <c r="D7" s="21">
-        <f>COUNTIF('3 전달·조치·확인'!$G$4:$G$19,"실패")</f>
+        <f>COUNTIF('3 전달·조치·확인'!$G$4:$G$18,"실패")</f>
         <v>0</v>
       </c>
       <c r="E7" s="21">
-        <f>COUNTIF('3 전달·조치·확인'!$G$4:$G$19,"오류")</f>
+        <f>COUNTIF('3 전달·조치·확인'!$G$4:$G$18,"오류")</f>
         <v>0</v>
       </c>
       <c r="F7" s="21">
-        <f>COUNTIF('3 전달·조치·확인'!$G$4:$G$19,"보류")</f>
+        <f>COUNTIF('3 전달·조치·확인'!$G$4:$G$18,"보류")</f>
         <v>0</v>
       </c>
       <c r="G7" s="21">
-        <f>COUNTIF('3 전달·조치·확인'!$G$4:$G$19,"확인 불가")</f>
+        <f>COUNTIF('3 전달·조치·확인'!$G$4:$G$18,"확인 불가")</f>
         <v>0</v>
       </c>
       <c r="H7" s="21">
-        <f>COUNTIF('3 전달·조치·확인'!$G$4:$G$19,"문의")</f>
+        <f>COUNTIF('3 전달·조치·확인'!$G$4:$G$18,"문의")</f>
         <v>0</v>
       </c>
       <c r="I7" s="21">
-        <f>COUNTBLANK('3 전달·조치·확인'!$G$4:$G$19)</f>
-        <v>16</v>
+        <f>COUNTBLANK('3 전달·조치·확인'!$G$4:$G$18)</f>
+        <v>15</v>
       </c>
       <c r="J7" s="22">
         <f>IF(B7=0,0,(B7-I7)/B7)</f>
@@ -1705,36 +2131,36 @@
         </is>
       </c>
       <c r="B8" s="21">
-        <f>COUNTA('4 공문·결재'!$A$4:$A$9)</f>
-        <v>6</v>
+        <f>COUNTA('4 공문·결재'!$A$4:$A$10)</f>
+        <v>7</v>
       </c>
       <c r="C8" s="21">
-        <f>COUNTIF('4 공문·결재'!$G$4:$G$9,"성공")</f>
+        <f>COUNTIF('4 공문·결재'!$G$4:$G$10,"성공")</f>
         <v>0</v>
       </c>
       <c r="D8" s="21">
-        <f>COUNTIF('4 공문·결재'!$G$4:$G$9,"실패")</f>
+        <f>COUNTIF('4 공문·결재'!$G$4:$G$10,"실패")</f>
         <v>0</v>
       </c>
       <c r="E8" s="21">
-        <f>COUNTIF('4 공문·결재'!$G$4:$G$9,"오류")</f>
+        <f>COUNTIF('4 공문·결재'!$G$4:$G$10,"오류")</f>
         <v>0</v>
       </c>
       <c r="F8" s="21">
-        <f>COUNTIF('4 공문·결재'!$G$4:$G$9,"보류")</f>
+        <f>COUNTIF('4 공문·결재'!$G$4:$G$10,"보류")</f>
         <v>0</v>
       </c>
       <c r="G8" s="21">
-        <f>COUNTIF('4 공문·결재'!$G$4:$G$9,"확인 불가")</f>
+        <f>COUNTIF('4 공문·결재'!$G$4:$G$10,"확인 불가")</f>
         <v>0</v>
       </c>
       <c r="H8" s="21">
-        <f>COUNTIF('4 공문·결재'!$G$4:$G$9,"문의")</f>
+        <f>COUNTIF('4 공문·결재'!$G$4:$G$10,"문의")</f>
         <v>0</v>
       </c>
       <c r="I8" s="21">
-        <f>COUNTBLANK('4 공문·결재'!$G$4:$G$9)</f>
-        <v>6</v>
+        <f>COUNTBLANK('4 공문·결재'!$G$4:$G$10)</f>
+        <v>7</v>
       </c>
       <c r="J8" s="22">
         <f>IF(B8=0,0,(B8-I8)/B8)</f>
@@ -1792,7 +2218,7 @@
       </c>
       <c r="B10" s="24">
         <f>SUM(B5:B9)</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C10" s="24">
         <f>SUM(C5:C9)</f>
@@ -1820,7 +2246,7 @@
       </c>
       <c r="I10" s="24">
         <f>SUM(I5:I9)</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J10" s="25">
         <f>IF(B10=0,0,(B10-I10)/B10)</f>
@@ -1871,7 +2297,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -1891,7 +2317,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>🗂 새 탭에서 시작하세요. 1~4번 시트는 이 탭 하나에서 이어서 합니다(탭을 닫거나 새 탭을 열면 처음 상태로 돌아갑니다).</t>
+          <t>🗂 1~6번은 모두 각자 하고, 만들기 창은 [취소]로 닫습니다 — [생성]은 진행자만 누릅니다. 6번까지 끝나면 단체방에 «만들기 전 확인 끝».</t>
         </is>
       </c>
     </row>
@@ -1948,7 +2374,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1956,7 +2382,7 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>올해 평가가 없을 때 첫 화면</t>
         </is>
@@ -1982,7 +2408,7 @@
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C5" s="30" t="inlineStr">
@@ -1990,7 +2416,7 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>지난해 평가 보기</t>
         </is>
@@ -2004,20 +2430,20 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2025년 평가가 보이고 요약 숫자가 표 내용과 맞다</t>
+          <t>2025년 평가가 보이고 요약 숫자가 표 내용과 맞다. 2025년 자료가 없으면 «확인 불가»</t>
         </is>
       </c>
       <c r="G5" s="29" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
     </row>
-    <row r="6" ht="51" customHeight="1">
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="28" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>하정수 → 홍길동 → 김담양</t>
+          <t>QA하정수6(담당 공무원)</t>
         </is>
       </c>
       <c r="C6" s="30" t="inlineStr">
@@ -2025,32 +2451,32 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>담당자가 아니면 만들 수 없다</t>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>담당 공무원은 만들 수 없다</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>계정을 차례로 바꿔 2026년 화면을 본다</t>
+          <t>QA하정수6 창에서 같은 화면을 본다</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>세 계정 모두 [＋ 정기평가 생성]이 없고 «조회 전용 — … 재난안전과 담당자가 생성합니다» 안내가 보인다</t>
+          <t>[＋ 정기평가 생성]이 없고, 재난안전과 담당자가 만든다는 안내가 보인다</t>
         </is>
       </c>
       <c r="G6" s="29" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
     </row>
-    <row r="7" ht="51" customHeight="1">
+    <row r="7" ht="81" customHeight="1">
       <c r="A7" s="28" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C7" s="30" t="inlineStr">
@@ -2058,16 +2484,17 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>만들기 1단계 — 대상 부서 고르기</t>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>만들기 창 — 대상 부서 고르기</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
           <t>① [＋ 정기평가 생성]
-② 부서 몇 개를 체크 해제했다가 다시 체크
-③ 검색창에 부서 이름 일부를 친다</t>
+② 부서 몇 개를 체크 해제했다가 다시 체크한다
+③ 검색창에 내 부서 이름 일부를 친다
+④ [취소]</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -2079,13 +2506,13 @@
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="66" customHeight="1">
       <c r="A8" s="28" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C8" s="30" t="inlineStr">
@@ -2093,15 +2520,17 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>부서를 하나도 안 고르면 막힌다</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>① 전체 선택을 해제한다
-② [다음]</t>
+          <t>① [＋ 정기평가 생성]
+② 전체 선택을 해제한다
+③ [다음]
+④ [취소]</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -2113,13 +2542,13 @@
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="7" t="n"/>
     </row>
-    <row r="9" ht="51" customHeight="1">
+    <row r="9" ht="66" customHeight="1">
       <c r="A9" s="28" t="n">
         <v>6</v>
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
@@ -2127,15 +2556,17 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>점검일자가 없으면 막힌다</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>① 물순환사업소를 포함해 부서를 고르고 [다음]
-② 점검일자를 비운 채 [생성]</t>
+          <t>① [＋ 정기평가 생성]
+② 내 부서(문화체육과)가 체크된 채 [다음]
+③ 점검일자를 비운 채 [생성]
+④ [취소]</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -2147,13 +2578,14 @@
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="7" t="n"/>
     </row>
-    <row r="10" ht="51" customHeight="1">
+    <row r="10" ht="141" customHeight="1">
       <c r="A10" s="28" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="30" t="inlineStr">
-        <is>
-          <t>박안전</t>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)
+진행자만</t>
         </is>
       </c>
       <c r="C10" s="30" t="inlineStr">
@@ -2161,21 +2593,23 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>점검일자를 넣고 만들기</t>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>평가 만들기</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>① 일괄 점검일자를 넣고 적용
-② 한 부서만 다른 날짜로 바꾼다
-③ [생성]</t>
+          <t>모두 «만들기 전 확인 끝»을 알리면 ① [＋ 정기평가 생성]
+② 전체 선택을 해제하고 물순환사업소 · 건설과 · 공공시설사업소 · 담양읍 · 보건소 · 문화체육과 · 환경과 7개만 체크한다
+③ 일괄 점검일자를 넣어 적용하고 한 부서만 다른 날짜로 바꾼다
+④ [생성]
+⑤ 단체방에 «평가 만듦»</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>평가가 만들어지고 고른 부서가 모두 표에 있다. 바꾼 부서는 그 날짜로 들어가 있다</t>
+          <t>평가가 만들어지고 7개 부서가 표에 있다. 바꾼 부서는 그 날짜로 들어가 있다</t>
         </is>
       </c>
       <c r="G10" s="29" t="n"/>
@@ -2186,9 +2620,9 @@
       <c r="A11" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="30" t="inlineStr">
-        <is>
-          <t>박안전</t>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C11" s="30" t="inlineStr">
@@ -2196,32 +2630,32 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>새로고침해도 그대로</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>브라우저 새로고침(F5)</t>
+          <t>«평가 만듦»이 오면 브라우저 새로고침(F5)</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>제목 «2026년 정기 위험성평가»와 부서·점검일이 그대로다. 오른쪽 위에는 «정기평가는 연 1회 등록 원칙»이 보인다</t>
+          <t>«2026년 정기 위험성평가» 제목과 7개 부서·점검일이 보인다. 오른쪽 위에 «정기평가는 연 1회 등록 원칙»이 보인다</t>
         </is>
       </c>
       <c r="G11" s="29" t="n"/>
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
     </row>
-    <row r="12" ht="36" customHeight="1">
+    <row r="12" ht="51" customHeight="1">
       <c r="A12" s="28" t="n">
         <v>9</v>
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C12" s="30" t="inlineStr">
@@ -2229,20 +2663,19 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>단계별 안내 켜 보기</t>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>로그인 남은 시간</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>① 화면 위 «단계별 안내 시작»
-② 안내를 읽고 [안내 닫기]</t>
+          <t>화면 맨 위에 로그인 남은 시간이 보이는지 본다. 30분이 지나 끊기면 다시 로그인한다</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>지금 할 단계와 눌러야 할 버튼을 짚어 주고, 닫으면 사라진다</t>
+          <t>남은 시간이 보이고, 30분이 지나면 로그인 화면으로 간다. 다시 로그인하면 이어서 할 수 있다</t>
         </is>
       </c>
       <c r="G12" s="29" t="n"/>
@@ -2297,11 +2730,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -2321,7 +2754,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>🗂 앞 시트와 같은 탭에서 이어서 하세요. 1번 시트에서 만든 2026년 평가를 씁니다.</t>
+          <t>🗂 진행자가 «양식 올림»을 알리면 시작합니다. 내 부서 제출은 각자 하고, 보고서는 진행자가 올립니다.</t>
         </is>
       </c>
     </row>
@@ -2372,13 +2805,14 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="51" customHeight="1">
+    <row r="4" ht="66" customHeight="1">
       <c r="A4" s="28" t="n">
         <v>10</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)
+진행자만</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2386,7 +2820,7 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>설문조사표 양식 올리기</t>
         </is>
@@ -2394,26 +2828,27 @@
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>① 설문조사표 공통 양식을 첨부한다
-② 한 부서에만 다른 양식을 첨부한다
-③ 새로고침</t>
+② 환경과에만 다른 양식을 첨부한다
+③ 새로고침
+④ 단체방에 «양식 올림»</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>공통 양식이 전 부서에, 따로 올린 부서에는 그 양식이 붙는다. 새로고침해도 파일 이름이 남는다</t>
+          <t>공통 양식이 전 부서에, 환경과에는 따로 올린 양식이 붙는다. 새로고침해도 파일 이름이 남는다</t>
         </is>
       </c>
       <c r="G4" s="29" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="66" customHeight="1">
       <c r="A5" s="28" t="n">
         <v>11</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA하정수6(담당 공무원)</t>
         </is>
       </c>
       <c r="C5" s="30" t="inlineStr">
@@ -2421,32 +2856,35 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>부서가 작성본을 낸다</t>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>내 부서가 작성본을 낸다</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>내 부서 진행 카드에서 작성본을 제출한다</t>
+          <t>«양식 올림»이 오면 ① 내 부서 진행 카드에 공통 양식이 있는지 본다
+② 작성본을 제출한다
+③ 단체방에 «제출 끝»</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>제출자·제출일이 남고 표의 «제출본» 칸에 바로 보인다. 다른 부서 줄에는 제출 버튼이 없다</t>
+          <t>제출자(QA하정수6)·제출일이 남고 표의 «제출본» 칸에 바로 보인다. 다른 부서 줄에는 제출 버튼이 없다</t>
         </is>
       </c>
       <c r="G5" s="29" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
     </row>
-    <row r="6" ht="36" customHeight="1">
+    <row r="6" ht="51" customHeight="1">
       <c r="A6" s="28" t="n">
         <v>12</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)
+진행자만</t>
         </is>
       </c>
       <c r="C6" s="30" t="inlineStr">
@@ -2454,14 +2892,14 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>재난안전과가 대신 올린다</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>아직 안 낸 부서의 제출본을 «대리 등록»한다</t>
+          <t>환경과의 제출본을 «대리 등록»한다</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -2473,13 +2911,14 @@
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
     </row>
-    <row r="7" ht="36" customHeight="1">
+    <row r="7" ht="51" customHeight="1">
       <c r="A7" s="28" t="n">
         <v>13</v>
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)
+진행자만</t>
         </is>
       </c>
       <c r="C7" s="30" t="inlineStr">
@@ -2487,14 +2926,14 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>용역 보고서 올리기</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>① 통합 보고서를 첨부한다
+          <t>모두 «제출 끝»을 알리면 ① 통합 보고서를 첨부한다
 ② 새로고침</t>
         </is>
       </c>
@@ -2507,13 +2946,14 @@
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="66" customHeight="1">
       <c r="A8" s="28" t="n">
         <v>14</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>하정수 → 박안전</t>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)
+진행자만</t>
         </is>
       </c>
       <c r="C8" s="30" t="inlineStr">
@@ -2521,33 +2961,35 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>보고서를 올린 뒤에는 설문조사표를 못 바꾼다</t>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>내용이 빈 행은 전달되지 않는다</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>① 하정수로 제출본 바꾸기를 시도한다
-② 박안전으로 양식 바꾸기를 시도한다</t>
+          <t>① 환경과에 [＋ 행 추가]
+② 유해위험요인만 적고 개선조치는 비워 둔다
+③ [부서 전달]을 눌러 본다
+④ 창을 닫고 단체방에 «보고서 올림»</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>«보고서가 등록되어 … 더 이상 바꿀 수 없습니다»가 뜨고 파일은 «🔒 열람»으로만 남는다</t>
+          <t>«유효한 항목이 있는 부서가 없습니다. 요인명·개선조치를 채워주세요.»가 뜬다</t>
         </is>
       </c>
       <c r="G8" s="29" t="n"/>
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="7" t="n"/>
     </row>
-    <row r="9" ht="51" customHeight="1">
+    <row r="9" ht="66" customHeight="1">
       <c r="A9" s="28" t="n">
         <v>15</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA하정수6(담당 공무원) → QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
@@ -2555,21 +2997,20 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>내용이 빈 행은 전달되지 않는다</t>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>보고서를 올린 뒤에는 설문조사표를 못 바꾼다</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>① 한 부서에 [＋ 행 추가]
-② 유해위험요인만 적고 개선조치는 비운다
-③ 부서 전달을 눌러 본다</t>
+          <t>«보고서 올림»이 오면 ① QA하정수6 창에서 내 부서 제출본 바꾸기를 시도한다
+② QA박안전6 창에서 내 부서 양식 바꾸기를 시도한다</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>«유효한 항목이 있는 부서가 없습니다. 요인명·개선조치를 채워주세요.»가 뜬다</t>
+          <t>«보고서가 등록되어 … 더 이상 바꿀 수 없습니다»가 뜨고 파일은 «🔒 열람»으로만 남는다</t>
         </is>
       </c>
       <c r="G9" s="29" t="n"/>
@@ -2580,9 +3021,9 @@
       <c r="A10" s="28" t="n">
         <v>16</v>
       </c>
-      <c r="B10" s="30" t="inlineStr">
-        <is>
-          <t>박안전</t>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C10" s="30" t="inlineStr">
@@ -2590,19 +3031,19 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>부서별 개선조치 적기</t>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>내 부서 개선조치 적기</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>물순환사업소를 포함해 두 부서에 유해위험요인·원인·개선조치·담당자를 채운 행을 하나씩 만든다</t>
+          <t>내 부서(문화체육과) 줄에 유해위험요인·원인·개선조치·담당자(QA하정수6)를 채운 행 3개를 만든다</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>적은 행이 저장된다</t>
+          <t>적은 행 3개가 저장된다</t>
         </is>
       </c>
       <c r="G10" s="29" t="n"/>
@@ -2615,7 +3056,7 @@
       </c>
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C11" s="30" t="inlineStr">
@@ -2623,14 +3064,14 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>시설물 칸 3가지 상태</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>행 3개 중 ① 하나는 시설물을 지정
+          <t>16번의 행 3개 중 ① 하나는 시설물을 지정
 ② 하나는 [해당 없음]
 ③ 하나는 그대로 둔다</t>
         </is>
@@ -2644,13 +3085,13 @@
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
     </row>
-    <row r="12" ht="51" customHeight="1">
+    <row r="12" ht="96" customHeight="1">
       <c r="A12" s="28" t="n">
         <v>18</v>
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -2658,7 +3099,7 @@
           <t>관리대상 &gt; 시설물 위험도</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>시설물에서 넘어와 행 추가</t>
         </is>
@@ -2666,7 +3107,9 @@
       <c r="E12" s="3" t="inlineStr">
         <is>
           <t>① 점수가 있는 시설물의 [근로자 위험성평가 연계]
-② 넘어간 화면에서 부서의 [＋ 행 추가]</t>
+② 넘어간 화면에서 내 부서의 [＋ 행 추가]
+③ 개선조치는 비워 둔다(이 행은 전달되지 않는다)
+④ 단체방에 «개선조치 적음»</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -2684,7 +3127,7 @@
       </c>
       <c r="B13" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -2692,33 +3135,67 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>보고서 취소 전에 한 번 묻는다</t>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>여럿이 적어도 내 행이 남는다</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>① [보고서 취소·재업로드]
-② 확인 창 문구를 읽고 [취소] (실행하지 마세요 — 적은 개선조치가 지워집니다)</t>
+          <t>모두 «개선조치 적음»을 알리면 새로고침 → 내 부서 줄과 다른 부서 줄을 본다</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>확인 창이 지워질 범위(부서 수·건수)를 알려 주고, [취소]하면 그대로다</t>
+          <t>16번에 적은 3행이 그대로이고 다른 사람이 적은 부서의 행도 보인다. 내 행이 사라졌거나 다른 값으로 바뀌었으면 «실패»</t>
         </is>
       </c>
       <c r="G13" s="29" t="n"/>
       <c r="H13" s="7" t="n"/>
       <c r="I13" s="7" t="n"/>
     </row>
+    <row r="14" ht="51" customHeight="1">
+      <c r="A14" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)
+진행자만</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>위험성평가 &gt; 정기 위험성평가</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>보고서 취소 전에 한 번 묻는다</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>① [보고서 취소·재업로드]
+② 확인 창 문구를 읽고 [취소] (실행하지 마세요 — 6명이 적은 개선조치가 모두 지워집니다)</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>확인 창이 지워질 범위(부서 수·건수)를 알려 주고, [취소]하면 그대로다</t>
+        </is>
+      </c>
+      <c r="G14" s="29" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:I13"/>
+  <autoFilter ref="A3:I14"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G4:G13">
+  <conditionalFormatting sqref="G4:G14">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
       <formula>"성공"</formula>
     </cfRule>
@@ -2738,13 +3215,13 @@
       <formula>"문의"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H13">
+  <conditionalFormatting sqref="H4:H14">
     <cfRule type="expression" priority="7" dxfId="7">
       <formula>AND(OR($G4="실패",$G4="오류",$G4="문의"),$H4="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G4:G13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르세요" error="결과는 성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중 하나입니다." promptTitle="결과 고르기" prompt="성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중에서 고르세요. 실패·오류·문의면 옆 메모에 한 줄." type="list">
+    <dataValidation sqref="G4:G14" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르세요" error="결과는 성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중 하나입니다." promptTitle="결과 고르기" prompt="성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중에서 고르세요. 실패·오류·문의면 옆 메모에 한 줄." type="list">
       <formula1>"성공,실패,오류,보류,확인 불가,문의"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2760,11 +3237,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -2784,7 +3261,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>🗂 앞 시트와 같은 탭에서 이어서 하세요.</t>
+          <t>🗂 진행자가 «전달함»을 알리면 시작합니다. 내 부서 일은 QA박안전6 창과 QA하정수6 창을 번갈아 씁니다.</t>
         </is>
       </c>
     </row>
@@ -2835,13 +3312,14 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
+    <row r="4" ht="51" customHeight="1">
       <c r="A4" s="28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)
+진행자만</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2849,14 +3327,14 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>조치기한 없이 전달하면 막힌다</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>① 부서 전달
+          <t>모두 «개선조치 적음»을 알리면 ① [부서 전달]
 ② 기한을 비운 채 [전달 실행]</t>
         </is>
       </c>
@@ -2871,11 +3349,12 @@
     </row>
     <row r="5" ht="66" customHeight="1">
       <c r="A5" s="28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)
+진행자만</t>
         </is>
       </c>
       <c r="C5" s="30" t="inlineStr">
@@ -2883,34 +3362,35 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>부서로 전달하기</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>① 일괄 기한 2026-08-31
-② 물순환사업소가 아닌 한 부서만 2026-07-10 으로 바꾼다
-③ [전달 실행]</t>
+          <t>① 일괄 기한을 오늘부터 30일 뒤로
+② 한 부서만 60일 뒤로 바꾼다
+③ [전달 실행]
+④ 단체방에 «전달함»</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>«N개 부서에 개선조치 M건 전달»이 뜨고 표가 전달 상태로 바뀐다. 개선조치가 없는 부서는 자동으로 빠진다</t>
+          <t>«N개 부서에 개선조치 M건 전달»이 뜨고 표가 전달 상태로 바뀐다. 개선조치가 빈 행뿐인 부서(환경과)는 자동으로 빠진다</t>
         </is>
       </c>
       <c r="G5" s="29" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
     </row>
-    <row r="6" ht="36" customHeight="1">
+    <row r="6" ht="51" customHeight="1">
       <c r="A6" s="28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA하정수6(담당 공무원) → QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C6" s="30" t="inlineStr">
@@ -2918,166 +3398,167 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>부서 담당자는 자기 부서만 본다</t>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>누가 어느 부서를 보나</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>부서별 조치 표를 본다</t>
+          <t>«전달함»이 오면 ① QA하정수6 창에서 부서별 조치 표를 본다
+② QA박안전6 창에서 같은 표를 본다</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>물순환사업소 줄만 보이고 다른 부서를 열 수단이 없다</t>
+          <t>QA하정수6 계정에는 내 부서 줄만 보이고 다른 부서를 열 수단이 없다. QA박안전6 계정에는 대상 부서가 다 보인다</t>
         </is>
       </c>
       <c r="G6" s="29" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
     </row>
-    <row r="7" ht="36" customHeight="1">
+    <row r="7" ht="51" customHeight="1">
       <c r="A7" s="28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>정환경</t>
-        </is>
-      </c>
-      <c r="C7" s="30" t="inlineStr">
-        <is>
-          <t>위험성평가 &gt; 정기 위험성평가</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>다른 부서 담당자도 자기 부서만</t>
+          <t>QA하정수6(담당 공무원)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>대시보드 &gt; 내 할일</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>조치 완료는 사진·내용·서명이 있어야</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>부서별 조치 표를 본다</t>
+          <t>① 개선조치 하나의 완료 처리를 연다
+② 사진 없이 저장 → 사진만 넣고 저장 → 내용까지 넣고 서명 없이 저장</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>환경과 것만 보이고 물순환사업소 건의 버튼이 없다</t>
+          <t>차례로 «개선 후 사진을…» «조치 내용을 입력하세요.» «완료 확인 서명(이름)을…»으로 막힌다. 적은 값은 남아 있다</t>
         </is>
       </c>
       <c r="G7" s="29" t="n"/>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
     </row>
-    <row r="8" ht="51" customHeight="1">
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="28" t="n">
-        <v>24</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>하정수</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
+        <v>25</v>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>QA하정수6(담당 공무원)</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>대시보드 &gt; 내 할일</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>조치 완료는 사진·내용·서명이 있어야</t>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>조치 완료하기</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>① 개선조치의 완료 처리를 연다
-② 사진 없이 저장 → 사진만 넣고 저장 → 내용까지 넣고 서명 없이 저장</t>
+          <t>사진·내용·서명을 모두 채워 완료 → 하나 더 완료(3건 중 2건)</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>차례로 «개선 후 사진을…» «조치 내용을 입력하세요.» «완료 확인 서명(이름)을…»으로 막힌다. 적은 값은 남아 있다</t>
+          <t>완료되고 «확인 대기»가 붙는다. 내 할일에는 내 부서 건만 있다</t>
         </is>
       </c>
       <c r="G8" s="29" t="n"/>
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="7" t="n"/>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="51" customHeight="1">
       <c r="A9" s="28" t="n">
-        <v>25</v>
-      </c>
-      <c r="B9" s="30" t="inlineStr">
-        <is>
-          <t>하정수</t>
-        </is>
-      </c>
-      <c r="C9" s="30" t="inlineStr">
-        <is>
-          <t>대시보드 &gt; 내 할일</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>조치 완료하기</t>
+        <v>26</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>위험성평가 &gt; 정기 위험성평가</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>담당자·기한을 바꿀 땐 사유가 필요</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>사진·내용·서명을 모두 채워 완료 → 같은 부서 건을 하나 더 완료</t>
+          <t>내 부서 상세에서 아직 완료하지 않은 1건의 기한을 어제로 바꾼다 ① 사유 없이 저장
+② 사유를 넣고 저장</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>완료되고 «확인 대기»가 붙는다</t>
+          <t>사유 없이는 «변경 사유를 입력하세요.» 저장하면 이력에 «기한 A → B — 사유»가 남고 그 건이 기한 초과로 보인다</t>
         </is>
       </c>
       <c r="G9" s="29" t="n"/>
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="7" t="n"/>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="51" customHeight="1">
       <c r="A10" s="28" t="n">
-        <v>26</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
+        <v>27</v>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>담당자·기한을 바꿀 땐 사유가 필요</t>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>기한 지난 건 재촉</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>① 부서 상세에서 담당자나 기한을 바꾼다
-② 사유 없이 저장 → 사유를 넣고 저장</t>
+          <t>26번 건의 [재촉]</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>사유 없이는 «변경 사유를 입력하세요.» 저장하면 이력에 «기한 A → B — 사유»가 남는다</t>
+          <t>«재촉 알림을 발송했습니다», 이력에 보낸 사람이 QA박안전6 계정으로 남는다. 완료한 건에는 재촉 버튼이 없다</t>
         </is>
       </c>
       <c r="G10" s="29" t="n"/>
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="7" t="n"/>
     </row>
-    <row r="11" ht="51" customHeight="1">
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B11" s="30" t="inlineStr">
-        <is>
-          <t>박안전</t>
+        <v>28</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>QA하정수6(담당 공무원)</t>
         </is>
       </c>
       <c r="C11" s="30" t="inlineStr">
@@ -3085,32 +3566,32 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>기한 지난 부서 재촉</t>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>담당 공무원에게는 확인·재촉 버튼이 없다</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>기한 2026-07-10 부서의 상세 → [재촉]</t>
+          <t>QA하정수6 창에서 내 부서 상세를 연다</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>«재촉 알림을 발송했습니다», 이력에 보낸 사람이 박안전으로 남는다. 완료한 건에는 재촉 버튼이 없다</t>
+          <t>볼 수는 있지만 [재촉]·[확인]·[반려]가 없다</t>
         </is>
       </c>
       <c r="G11" s="29" t="n"/>
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="51" customHeight="1">
       <c r="A12" s="28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>김담양</t>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C12" s="30" t="inlineStr">
@@ -3118,32 +3599,34 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>군수는 재촉하지 않는다</t>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>완료 확인 — 열람 체크를 해야 확인된다</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>기한 지난 부서의 상세를 연다</t>
+          <t>① 내 부서 상세의 확인 대기 카드 하나
+② 체크 없이 [확인]
+③ «…열람했습니다»를 체크하고 [확인]</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>볼 수는 있지만 [재촉] 버튼이 없다</t>
+          <t>체크 전에는 [확인]이 눌리지 않는다. 확인하면 «확인 완료»가 된다</t>
         </is>
       </c>
       <c r="G12" s="29" t="n"/>
       <c r="H12" s="7" t="n"/>
       <c r="I12" s="7" t="n"/>
     </row>
-    <row r="13" ht="36" customHeight="1">
+    <row r="13" ht="51" customHeight="1">
       <c r="A13" s="28" t="n">
-        <v>29</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>오순환</t>
+        <v>30</v>
+      </c>
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C13" s="30" t="inlineStr">
@@ -3151,19 +3634,20 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>부서장은 자기 부서를 본다</t>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>반려는 사유가 있어야</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>진행 상황을 본다</t>
+          <t>내 부서의 다른 확인 대기 건을 ① 사유 없이 반려
+② 사유를 넣고 반려</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>물순환사업소만 보이고 제출·완료 같은 버튼이 없다</t>
+          <t>사유 없이는 «반려 사유를 입력하세요 — …»로 막히고, 반려하면 카드에 사유와 회차가 보인다</t>
         </is>
       </c>
       <c r="G13" s="29" t="n"/>
@@ -3172,33 +3656,33 @@
     </row>
     <row r="14" ht="51" customHeight="1">
       <c r="A14" s="28" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="C14" s="30" t="inlineStr">
-        <is>
-          <t>위험성평가 &gt; 정기 위험성평가</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>완료 확인 — 열람 체크를 해야 확인된다</t>
+          <t>QA하정수6(담당 공무원)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>대시보드 &gt; 내 할일</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>반려된 건을 다시 낸다</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>① 물순환사업소 부서 상세의 확인 대기 카드
-② 체크 없이 [확인]
-③ «…열람했습니다»를 체크하고 [확인]</t>
+          <t>① 내 할일에 반려 건이 다시 떠 있는지 본다
+② [재제출]로 다시 완료
+③ 26번에서 기한을 바꾼 건도 완료한다</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>체크 전에는 [확인]이 눌리지 않는다. 확인하면 «확인 완료»가 된다</t>
+          <t>반려 건이 할 일에 다시 있고 사유가 보인다. 재제출하면 «확인 대기»로 돌아간다</t>
         </is>
       </c>
       <c r="G14" s="29" t="n"/>
@@ -3207,32 +3691,31 @@
     </row>
     <row r="15" ht="51" customHeight="1">
       <c r="A15" s="28" t="n">
-        <v>31</v>
-      </c>
-      <c r="B15" s="30" t="inlineStr">
-        <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="C15" s="30" t="inlineStr">
+        <v>32</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>반려는 사유가 있어야</t>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>확인이 덜 끝나면 공문을 못 쓴다</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>다른 확인 대기 건을 ① 사유 없이 반려
-② 사유를 넣고 반려</t>
+          <t>공문(온나라 이관) 영역을 본다</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>사유 없이는 «반려 사유를 입력하세요 — …»로 막히고, 반려하면 카드에 사유와 회차가 보인다</t>
+          <t>«전 건 확인 완료 후 기안할 수 있습니다 (확인 대기 N건 · 반려 M건)»처럼 남은 건수를 알려 준다. 다른 사람 부서의 건도 함께 센다</t>
         </is>
       </c>
       <c r="G15" s="29" t="n"/>
@@ -3241,32 +3724,31 @@
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="28" t="n">
-        <v>32</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>하정수</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>대시보드 &gt; 내 할일</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>반려된 건을 다시 낸다</t>
+        <v>33</v>
+      </c>
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C16" s="30" t="inlineStr">
+        <is>
+          <t>위험성평가 &gt; 정기 위험성평가</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>내 부서 확인 마치기</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>① 내 할일에 반려 건이 다시 떠 있는지 본다
-② [재제출]로 다시 완료</t>
+          <t>내 부서의 확인 대기 건을 모두 확인한다 → 단체방에 «확인 끝»</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>반려 건이 할 일에 다시 있고 사유가 보인다. 재제출하면 «확인 대기»로 돌아간다</t>
+          <t>내 부서가 완료 부서로 세어진다</t>
         </is>
       </c>
       <c r="G16" s="29" t="n"/>
@@ -3275,31 +3757,31 @@
     </row>
     <row r="17" ht="51" customHeight="1">
       <c r="A17" s="28" t="n">
-        <v>33</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
+        <v>34</v>
+      </c>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C17" s="30" t="inlineStr">
         <is>
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>확인이 덜 끝나면 공문을 못 쓴다</t>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>전 부서 확인이 끝나면 공문을 쓸 수 있다</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>화면의 공문(온나라 이관) 영역을 본다</t>
+          <t>모두 «확인 끝»을 알리면 새로고침</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>«전 건 확인 완료 후 기안할 수 있습니다 (확인 대기 N건 · 반려 M건)»처럼 남은 건수를 알려 준다</t>
+          <t>모든 부서가 완료(또는 지적사항 없음)이고 공문 영역이 «전 부서 확인 완료 — 공문을 작성해…»로 바뀐다</t>
         </is>
       </c>
       <c r="G17" s="29" t="n"/>
@@ -3308,11 +3790,11 @@
     </row>
     <row r="18" ht="51" customHeight="1">
       <c r="A18" s="28" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B18" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C18" s="30" t="inlineStr">
@@ -3320,65 +3802,32 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>전 부서 확인 마치기</t>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>이력 탭</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>남은 확인 대기 건을 모두 확인한다(다른 부서의 조치 완료는 박안전이 대신 처리해도 된다)</t>
+          <t>[이력] 탭을 연다</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>완료 부서 수가 대상 부서 수와 같아지고 공문 영역이 «전 부서 확인 완료 — 공문을 작성해…»로 바뀐다</t>
+          <t>만들기·첨부·전달·재촉·변경·확인·반려가 시간순으로 있고, 누가 했는지 사람마다 다른 계정 이름으로 남아 있다</t>
         </is>
       </c>
       <c r="G18" s="29" t="n"/>
       <c r="H18" s="7" t="n"/>
       <c r="I18" s="7" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="28" t="n">
-        <v>35</v>
-      </c>
-      <c r="B19" s="30" t="inlineStr">
-        <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="C19" s="30" t="inlineStr">
-        <is>
-          <t>위험성평가 &gt; 정기 위험성평가</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>이력 탭</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>[이력] 탭을 연다</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>만들기·첨부·전달·재촉·변경·확인·반려가 시간순으로 모두 있다</t>
-        </is>
-      </c>
-      <c r="G19" s="29" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="7" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:I19"/>
+  <autoFilter ref="A3:I18"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G4:G19">
+  <conditionalFormatting sqref="G4:G18">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
       <formula>"성공"</formula>
     </cfRule>
@@ -3398,13 +3847,13 @@
       <formula>"문의"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H19">
+  <conditionalFormatting sqref="H4:H18">
     <cfRule type="expression" priority="7" dxfId="7">
       <formula>AND(OR($G4="실패",$G4="오류",$G4="문의"),$H4="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G4:G19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르세요" error="결과는 성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중 하나입니다." promptTitle="결과 고르기" prompt="성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중에서 고르세요. 실패·오류·문의면 옆 메모에 한 줄." type="list">
+    <dataValidation sqref="G4:G18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르세요" error="결과는 성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중 하나입니다." promptTitle="결과 고르기" prompt="성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중에서 고르세요. 실패·오류·문의면 옆 메모에 한 줄." type="list">
       <formula1>"성공,실패,오류,보류,확인 불가,문의"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3420,11 +3869,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -3444,7 +3893,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>🗂 앞 시트와 같은 탭에서 이어서 하세요. 위험성평가는 결재 결과를 «회신 등록»으로 옮겨 적습니다.</t>
+          <t>🗂 공문은 평가 1건에 하나라 진행자가 올립니다. 36번을 먼저 하고, «상신함»이 오면 38번부터 합니다. 상신하면 바로 «결재완료»(내부 처리)로 끝납니다 — 온나라로 가지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -3495,13 +3944,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="81" customHeight="1">
+    <row r="4" ht="111" customHeight="1">
       <c r="A4" s="28" t="n">
         <v>36</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3509,36 +3958,37 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t>공문 쓰기 → 미리보기 → 상신 순서</t>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>결재선 — 같은 사람을 두 번 못 넣는다</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>① [공문 기안]
-② 본문을 직접 쓴다(삽입 칩도 눌러 본다)
-③ 붙임을 고른다
-④ [문서 미리보기 →]
-⑤ [온나라로 결재 상신] → [상신]</t>
+② 결재선의 검토·결재 [조직도]에서 같은 사람을 두 번 고른다
+③ 한 칸을 비운 채 [문서 미리보기 →]로 가서 [온나라로 결재 상신]을 눌러 본다
+④ 상신하지 않고 창을 닫는다
+⑤ 단체방에 «결재선 확인 끝»</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>기안 화면에는 상신 버튼이 없고 미리보기에서만 상신한다. 본문은 자동으로 채워지지 않는다. 상신하면 문서번호가 붙고 «결재중»</t>
+          <t>이미 고른 사람과 기안자(QA박안전6)는 흐리게 보이고 고를 수 없다. 칸이 비면 상신이 막히고 이유가 나온다</t>
         </is>
       </c>
       <c r="G4" s="29" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
     </row>
-    <row r="5" ht="51" customHeight="1">
+    <row r="5" ht="141" customHeight="1">
       <c r="A5" s="28" t="n">
         <v>37</v>
       </c>
-      <c r="B5" s="30" t="inlineStr">
-        <is>
-          <t>박안전</t>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)
+진행자만</t>
         </is>
       </c>
       <c r="C5" s="30" t="inlineStr">
@@ -3546,33 +3996,38 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>결재선 — 같은 사람을 두 번 못 넣는다</t>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>공문 쓰기 → 미리보기 → 상신 순서</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>기안 화면의 결재선에서 ① 조직도로 검토·결재에 같은 사람을 고른다
-② 한 칸을 비우고 상신한다</t>
+          <t>모두 «결재선 확인 끝»을 알리면 ① [공문 기안]
+② 본문을 직접 쓴다(삽입 칩도 눌러 본다)
+③ 붙임을 고른다
+④ 결재선 검토·결재에 다른 두 사람의 박안전 계정을 고른다
+⑤ [문서 미리보기 →]
+⑥ [온나라로 결재 상신] → [상신]
+⑦ 단체방에 «상신함»</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>이미 고른 사람과 기안자는 흐리게 보이고 고를 수 없다. 칸이 비면 상신이 막히고 이유가 나온다</t>
+          <t>기안 화면에는 상신 버튼이 없고 미리보기에서만 상신한다. 본문은 자동으로 채워지지 않는다. 상신하면 바로 «결재완료»가 되고 경로가 «내부 처리»로 표시된다(결재자 칸은 비어 있다)</t>
         </is>
       </c>
       <c r="G5" s="29" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
     </row>
-    <row r="6" ht="66" customHeight="1">
+    <row r="6" ht="51" customHeight="1">
       <c r="A6" s="28" t="n">
         <v>38</v>
       </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>박안전</t>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C6" s="30" t="inlineStr">
@@ -3580,22 +4035,20 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>결재 결과 옮겨 적기</t>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>상신 뒤에는 잠긴다</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>① [결재 상태]
-② «결재 결과 회신 등록»
-③ 반려를 사유 없이 등록해 본다
-④ 검토 승인 → 결재 완료</t>
+          <t>«상신함»이 오면 ① 내 부서 상세에서 확인한 건을 확인 취소·반려해 본다
+② 단체방에 «잠김 확인 끝»</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>«연계 전 수동 기록»이라고 밝히고 처리자 이름이 결재선에서 나온다. 사유 없는 반려는 안 된다. 결재 완료면 평가가 끝난다</t>
+          <t>할 수 없고 잠긴 이유가 나온다</t>
         </is>
       </c>
       <c r="G6" s="29" t="n"/>
@@ -3606,9 +4059,9 @@
       <c r="A7" s="28" t="n">
         <v>39</v>
       </c>
-      <c r="B7" s="30" t="inlineStr">
-        <is>
-          <t>박안전</t>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>QA하정수6(담당 공무원)</t>
         </is>
       </c>
       <c r="C7" s="30" t="inlineStr">
@@ -3616,32 +4069,33 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>상신 뒤에는 잠긴다</t>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>담당 공무원에게는 공문 버튼이 없다</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>부서 상세에서 확인한 건을 확인 취소·반려해 본다</t>
+          <t>QA하정수6 창에서 같은 화면을 본다</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>할 수 없고 잠긴 이유가 나온다</t>
+          <t>[공문 기안]·[온나라로 결재 상신]이 없다</t>
         </is>
       </c>
       <c r="G7" s="29" t="n"/>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="66" customHeight="1">
       <c r="A8" s="28" t="n">
         <v>40</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>홍길동 → 김담양</t>
+          <t>QA박안전6(재난안전과)
+진행자만</t>
         </is>
       </c>
       <c r="C8" s="30" t="inlineStr">
@@ -3649,32 +4103,34 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>과장·군수에게는 공문 버튼이 없다</t>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>결재가 바로 끝난다</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>같은 화면을 본다</t>
+          <t>모두 «잠김 확인 끝»을 알리면 ① [결재 상태]를 연다
+② 결재 결과를 옮겨 적는 버튼이 있는지 본다
+③ 단체방에 «결재 완료 확인»</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>[공문 기안]·[상신]이 없고 결재 상태는 볼 수 있다</t>
+          <t>결재완료 · «내부 처리»로 보이고 37번에서 고른 결재선이 남아 있다. 결과를 옮겨 적는 버튼은 없다(있어서 누르면 막히면 «실패»). 평가가 끝난 상태다</t>
         </is>
       </c>
       <c r="G8" s="29" t="n"/>
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="7" t="n"/>
     </row>
-    <row r="9" ht="51" customHeight="1">
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="28" t="n">
         <v>41</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
@@ -3682,34 +4138,67 @@
           <t>위험성평가 &gt; 정기 위험성평가</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>지난 평가 둘러보기</t>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>끝난 평가</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>① 연도 2025
-② [문서 보기]·[결재 상태]·부서 상세를 연다
-③ 설문조사표 파일 이름을 누른다</t>
+          <t>«결재 완료 확인»이 오면 새로고침 → [결재 상태]를 연다</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>창이 잘 열린다. 파일은 «문서 뷰어는 전자문서 연계 후 제공됩니다»가 뜬다</t>
+          <t>평가가 끝난 상태로 보이고 결재 상태가 결재완료 · «내부 처리»다</t>
         </is>
       </c>
       <c r="G9" s="29" t="n"/>
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="7" t="n"/>
     </row>
+    <row r="10" ht="51" customHeight="1">
+      <c r="A10" s="28" t="n">
+        <v>42</v>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>QA박안전6(재난안전과)</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>위험성평가 &gt; 정기 위험성평가</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>지난 평가 둘러보기</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>① 연도를 2025로 바꾼다
+② [문서 보기]·[결재 상태]·부서 상세를 연다
+③ 설문조사표 파일 이름을 누른다</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>창이 잘 열린다. 파일은 열리거나 «…연계 후 제공됩니다» 안내가 뜬다. 2025년 자료가 없으면 «확인 불가»</t>
+        </is>
+      </c>
+      <c r="G10" s="29" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:I9"/>
+  <autoFilter ref="A3:I10"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G4:G9">
+  <conditionalFormatting sqref="G4:G10">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
       <formula>"성공"</formula>
     </cfRule>
@@ -3729,13 +4218,13 @@
       <formula>"문의"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H9">
+  <conditionalFormatting sqref="H4:H10">
     <cfRule type="expression" priority="7" dxfId="7">
       <formula>AND(OR($G4="실패",$G4="오류",$G4="문의"),$H4="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G4:G9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르세요" error="결과는 성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중 하나입니다." promptTitle="결과 고르기" prompt="성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중에서 고르세요. 실패·오류·문의면 옆 메모에 한 줄." type="list">
+    <dataValidation sqref="G4:G10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르세요" error="결과는 성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중 하나입니다." promptTitle="결과 고르기" prompt="성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중에서 고르세요. 실패·오류·문의면 옆 메모에 한 줄." type="list">
       <formula1>"성공,실패,오류,보류,확인 불가,문의"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3755,7 +4244,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -3775,7 +4264,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>🗂 새 탭에서 시작해도 됩니다. 수시 위험성평가는 부서가 사유가 생겨 올리고, 재난안전과 확인 단계가 없습니다.</t>
+          <t>🗂 각자 따로, 순서와 상관없이 해도 됩니다. 수시 위험성평가는 부서가 사유가 생겨 올리고 재난안전과 확인 단계가 없습니다. 다른 사람 것과 구분하려고 내용 앞에 내 이름을 붙입니다.</t>
         </is>
       </c>
     </row>
@@ -3828,11 +4317,11 @@
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="28" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA하정수6(담당 공무원)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3840,7 +4329,7 @@
           <t>위험성평가 &gt; 수시 위험성평가</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>등록은 실시 사유부터</t>
         </is>
@@ -3852,7 +4341,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>실시 사유를 먼저 고르게 하고, 부서는 물순환사업소로 고정돼 있다</t>
+          <t>실시 사유를 먼저 고르게 하고, 부서는 내 부서(문화체육과)로 고정돼 있다</t>
         </is>
       </c>
       <c r="G4" s="29" t="n"/>
@@ -3861,11 +4350,11 @@
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="28" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C5" s="30" t="inlineStr">
@@ -3873,14 +4362,14 @@
           <t>위험성평가 &gt; 수시 위험성평가</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>박안전은 부서를 고를 수 있다</t>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>재난안전과 담당자는 부서를 고를 수 있다</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>같은 등록 창을 연다</t>
+          <t>같은 등록 창을 연다 → [취소]</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -3894,11 +4383,11 @@
     </row>
     <row r="6" ht="51" customHeight="1">
       <c r="A6" s="28" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA하정수6(담당 공무원)</t>
         </is>
       </c>
       <c r="C6" s="30" t="inlineStr">
@@ -3906,7 +4395,7 @@
           <t>위험성평가 &gt; 수시 위험성평가</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>빈 칸이 있으면 등록되지 않는다</t>
         </is>
@@ -3928,11 +4417,11 @@
     </row>
     <row r="7" ht="81" customHeight="1">
       <c r="A7" s="28" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA하정수6(담당 공무원)</t>
         </is>
       </c>
       <c r="C7" s="30" t="inlineStr">
@@ -3940,7 +4429,7 @@
           <t>위험성평가 &gt; 수시 위험성평가</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>재해 사유면 칸이 더 생긴다</t>
         </is>
@@ -3963,11 +4452,11 @@
     </row>
     <row r="8" ht="51" customHeight="1">
       <c r="A8" s="28" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA하정수6(담당 공무원)</t>
         </is>
       </c>
       <c r="C8" s="30" t="inlineStr">
@@ -3975,7 +4464,7 @@
           <t>위험성평가 &gt; 수시 위험성평가</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>요인 행 추가·삭제</t>
         </is>
@@ -3998,11 +4487,11 @@
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="28" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA하정수6(담당 공무원)</t>
         </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
@@ -4010,14 +4499,14 @@
           <t>위험성평가 &gt; 수시 위험성평가</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>등록하면 개선조치가 생긴다</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>내용 QA_설비변경작업, 요인 2건으로 [등록] → 내 할일 확인</t>
+          <t>내용 «이혜린_설비변경작업», 요인 2건으로 [등록] → 내 할일 확인</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -4029,13 +4518,13 @@
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="7" t="n"/>
     </row>
-    <row r="10" ht="51" customHeight="1">
+    <row r="10" ht="66" customHeight="1">
       <c r="A10" s="28" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C10" s="30" t="inlineStr">
@@ -4043,14 +4532,14 @@
           <t>위험성평가 &gt; 수시 위험성평가</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>안전관리자 검토파일</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>① [＋ 검토파일 등록]
+          <t>48번의 «이혜린_설비변경작업» 건에서 ① [＋ 검토파일 등록]
 ② 파일명 비우고 → 검토자 이름 비우고 → 다 채워서 등록</t>
         </is>
       </c>
@@ -4065,11 +4554,11 @@
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="28" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA하정수6(담당 공무원)</t>
         </is>
       </c>
       <c r="C11" s="30" t="inlineStr">
@@ -4077,7 +4566,7 @@
           <t>위험성평가 &gt; 수시 위험성평가</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>검토파일은 재난안전과만</t>
         </is>
@@ -4098,11 +4587,11 @@
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="28" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C12" s="30" t="inlineStr">
@@ -4110,7 +4599,7 @@
           <t>위험성평가 &gt; 수시 위험성평가</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>검토파일 해제는 한 번 더 묻는다</t>
         </is>
@@ -4131,11 +4620,11 @@
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="28" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA하정수6(담당 공무원)</t>
         </is>
       </c>
       <c r="C13" s="30" t="inlineStr">
@@ -4143,7 +4632,7 @@
           <t>위험성평가 &gt; 수시 위험성평가</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>수시평가 개선조치 완료</t>
         </is>
@@ -4164,11 +4653,11 @@
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="28" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C14" s="30" t="inlineStr">
@@ -4176,7 +4665,7 @@
           <t>위험성평가 &gt; 수시 위험성평가</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>목록 조건</t>
         </is>
@@ -4188,20 +4677,20 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>조건대로 걸러지고 목록과 상세 내용이 같다</t>
+          <t>조건대로 걸러지고 목록과 상세 내용이 같다. 다른 사람이 올린 건도 보인다(정상)</t>
         </is>
       </c>
       <c r="G14" s="29" t="n"/>
       <c r="H14" s="7" t="n"/>
       <c r="I14" s="7" t="n"/>
     </row>
-    <row r="15" ht="36" customHeight="1">
+    <row r="15" ht="51" customHeight="1">
       <c r="A15" s="28" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>하정수 → 정환경 → 김담양</t>
+          <t>QA하정수6(담당 공무원) → QA박안전6(재난안전과)</t>
         </is>
       </c>
       <c r="C15" s="30" t="inlineStr">
@@ -4209,19 +4698,19 @@
           <t>위험성평가 &gt; 수시 위험성평가</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>누가 무엇을 보나</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>계정을 바꿔 가며 목록을 본다</t>
+          <t>두 창에서 목록을 본다</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>하정수·정환경은 자기 부서 건만 보인다. 김담양은 전부 보지만 등록·검토 버튼이 없다</t>
+          <t>QA하정수6 계정에는 내 부서 건만 보이고 다른 사람이 올린 건은 없다. QA박안전6 계정에는 전부 보인다</t>
         </is>
       </c>
       <c r="G15" s="29" t="n"/>
@@ -4346,7 +4835,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
